--- a/livrables/2026-09-04-roadmap-technique-septembre-eoleaf.xlsx
+++ b/livrables/2026-09-04-roadmap-technique-septembre-eoleaf.xlsx
@@ -611,7 +611,7 @@
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>A FAIRE</t>
+          <t>EN COURS</t>
         </is>
       </c>
       <c r="H3" s="6" t="inlineStr">
@@ -683,21 +683,21 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Page contact et formulaire SAV</t>
+          <t>Lien FAQ vers un formulaire SAV mort</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Rendre accessibles /fr/pages/contact (erreur client au crawl) et /fr/pages/formulaire-apres-vente (404, appelé depuis la FAQ), et vérifier les 12 versions linguistiques du gabarit. Une page contact injoignable sur un site qui vend en B2B coûte des demandes entrantes chaque jour. Fini quand : les 12 URL contact et les 12 URL SAV répondent 200, et le lien depuis la FAQ pointe vers l'URL vivante sans redirection intermédiaire.</t>
+          <t>Poser une 301 de /fr/pages/formulaire-apres-vente vers /fr/pages/formulaire-sav et corriger le lien depuis /fr/pages/faqs. Périmètre réduit par le contrôle Search Console du 04/09 : les pages contact FR, EN et DE sont indexées et saines, la FR est même en position 2,2 avec 477 impressions. Le crawl du 20/05 les déclarait en erreur à tort. Seule l'URL formulaire-apres-vente est réellement morte. Fini quand : /fr/pages/formulaire-apres-vente répond 301 vers formulaire-sav, et la FAQ pointe directement vers l'URL vivante.</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>SEO MONKEY + EOLEAF</t>
+          <t>EOLEAF</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>Nicolas / Eoleaf</t>
+          <t>Eoleaf</t>
         </is>
       </c>
     </row>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="F11" s="8" t="n">
-        <v>28</v>
+        <v>26.5</v>
       </c>
     </row>
   </sheetData>
@@ -1244,12 +1244,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>JSON-LD par gabarit</t>
+          <t>JSON-LD hors fiche produit</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Écrire et intégrer le balisage de données structurées prêt à coller : Product et Offer sur la fiche produit, Organization sur l'accueil, BreadcrumbList partout, FAQPage sur la FAQ, Article sur les pages métier. Rien n'a été posé à ce jour. Fini quand : le test des résultats enrichis ne remonte aucune erreur sur chacun des gabarits.</t>
+          <t>Écrire et intégrer le balisage de données structurées pour l'accueil (Organization, WebSite), la catégorie (CollectionPage, ItemList), les pages métier (Article, Person) et la FAQ (FAQPage). Périmètre réduit par le contrôle Search Console du 04/09 : la fiche produit porte déjà Product, Offer et AggregateRating, verdict PASS, avec extraits de produit, fiche de marchand et extraits d'avis détectés. Réserve : l'inspection d'URL ne remonte que les types éligibles aux résultats enrichis, l'absence de BreadcrumbList reste à confirmer dans le code des gabarits. Fini quand : le test des résultats enrichis ne remonte aucune erreur sur les quatre gabarits restants.</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -1258,7 +1258,7 @@
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         </is>
       </c>
       <c r="F9" s="8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" ht="104" customHeight="1">
@@ -1681,7 +1681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1730,17 +1730,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Pages relevées comme indexées au crawl du 20/05/2026</t>
+          <t>Pages portant au moins une impression sur 90 jours</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>2 994</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Incohérent avec les positions de l'onglet sémantique : à confronter à la Search Console.</t>
+          <t>Relevé Search Console du 04/09/2026 (03/06 au 01/09). Le crawl du 20/05 en déclarait 39 : il était faux.</t>
         </is>
       </c>
     </row>
@@ -1752,17 +1752,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>URL classées en erreur client au crawl du 20/05/2026</t>
+          <t>URL témoin déclarées indexées par Google</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>environ 250</t>
+          <t>10 sur 10</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Dont des pages positionnées de la 4e à la 8e place. Rejet Shopify sous charge suspecté.</t>
+          <t>Inspection d'URL du 04/09. Les 6 classées « erreur client » au crawl sont saines : robots autorisé, page récupérée, dernier passage de Google entre le 22/08 et le 04/09.</t>
         </is>
       </c>
     </row>
@@ -1774,17 +1774,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Versions linguistiques du site</t>
+          <t>Clics et impressions sur 90 jours</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>28 889 · 3 765 160</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>fr, en à la racine, da, de, es, fi, it, nl, no, pl, ro, sv. Une correction de gabarit se propage.</t>
+          <t>Position moyenne 12,5. Le site est massivement indexé et visible.</t>
         </is>
       </c>
     </row>
@@ -1796,17 +1796,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>URL anglaises servies sous le préfixe /fr</t>
+          <t>Part du français dans les clics</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>21 %</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Duplication et mauvaise langue déclarée. Défaut de l'application de traduction.</t>
+          <t>284 pages FR pour 6 106 clics. Les onze autres langues portent 79 % des clics : la priorisation par langue est à revoir avec Eoleaf.</t>
         </is>
       </c>
     </row>
@@ -1818,433 +1818,587 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Anciennes URL produit AEROPRO encore en circulation</t>
+          <t>Page la plus cliquée du site</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>/de/pages/kauf-eines-luftreinigers-fur-cannabis</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>La gamme a été renommée NeoPur, TeraPur, AltaPur sans que les 301 soient posées.</t>
+          <t>928 clics et 10 216 impressions sur 90 jours. Elle est en allemand.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="44" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Sémantique</t>
+          <t>Indexation</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Clusters FR où deux pages ou plus visent la même intention</t>
+          <t>URL témoin absentes du sitemap</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6 sur 10</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Le cluster tabac compte 5 pages, le dentaire 3, la voiture 4. Un pilier par cluster à désigner.</t>
+          <t>Dont l'accueil FR, la fiche AltaPur 700 et deux unités d'achat. Elles rankent sans être déclarées.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Sémantique</t>
+          <t>Indexation</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Requêtes de l'onglet sémantique planifiées sur plusieurs URL</t>
+          <t>URL déclarées au sitemap</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>4 au moins</t>
+          <t>3 001</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Voiture sur 3 URL, chambre sur 2, allergie chat sur 2, fumée de cigarette sur 2.</t>
+          <t>Dernier téléchargement par Google le 03/09/2026, zéro erreur, zéro avertissement.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="44" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Balisage</t>
+          <t>Sémantique</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Meta titles trop longs / trop courts / manquants</t>
+          <t>Écart de position relevé sur l'onglet sémantique</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>11 / 13 / 8</t>
+          <t>position 4 contre 37</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Une partie intégrée en juin et juillet, à recontrôler au re-crawl.</t>
+          <t>« purificateur d'air professionnel » : l'onglet donne 4, la Search Console 37 avec 894 impressions et 3 clics. Les positions de l'onglet sémantique sont à re-sourcer.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="44" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Balisage</t>
+          <t>JSON-LD</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Meta descriptions trop longues / manquantes</t>
+          <t>Fiche produit</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>15 / 12</t>
+          <t>Product, Offer et AggregateRating présents</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Aucune description trop courte relevée.</t>
+          <t>Verdict PASS au 04/09. Le gabarit qui encaisse est déjà équipé, contrairement au constat initial.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="44" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Balisage</t>
+          <t>Indexation</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>H1 trop longs / trop courts / manquants</t>
+          <t>Versions linguistiques du site</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>12 / 3 / 18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Les 18 manquants tiennent à 5 gabarits : 5 corrections, pas 18.</t>
+          <t>fr, en à la racine, da, de, es, fi, it, nl, no, pl, ro, sv. Une correction de gabarit se propage.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="44" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Balisage</t>
+          <t>Indexation</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Pages à deux H1 corrigées le 24/08/2026</t>
+          <t>URL anglaises servies sous le préfixe /fr</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>23 sur 23</t>
+          <t>36</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Vérifié : la colonne « H1 count now » est à 1 sur les 23 lignes.</t>
+          <t>Duplication et mauvaise langue déclarée. Défaut de l'application de traduction.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="44" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Balisage</t>
+          <t>Indexation</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Lignes PRODUITS du Tableau de balisage visant la mauvaise URL</t>
+          <t>Anciennes URL produit AEROPRO encore en circulation</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>6 sur 6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Elles ciblent les URL longues alors que les pages indexées sont les URL courtes.</t>
+          <t>La gamme a été renommée NeoPur, TeraPur, AltaPur sans que les 301 soient posées.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="44" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Images</t>
+          <t>Sémantique</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Images relevées et poids total</t>
+          <t>Clusters FR où deux pages ou plus visent la même intention</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>334 pour 91,3 Mo</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Moyenne de 273 Ko par image, très au-delà d'un gabarit e-commerce sain.</t>
+          <t>Le cluster tabac compte 5 pages, le dentaire 3, la voiture 4. Un pilier par cluster à désigner.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="44" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Images</t>
+          <t>Sémantique</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Images au-delà de 200 Ko / de 500 Ko</t>
+          <t>Requêtes de l'onglet sémantique planifiées sur plusieurs URL</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>64 / 36</t>
+          <t>4 au moins</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>La plus lourde atteint 3,58 Mo (PurCar_6.png).</t>
+          <t>Voiture sur 3 URL, chambre sur 2, allergie chat sur 2, fumée de cigarette sur 2.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="44" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Images</t>
+          <t>Balisage</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Formats servis</t>
+          <t>Meta titles trop longs / trop courts / manquants</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>232 jpeg, 99 png, 3 svg</t>
+          <t>11 / 13 / 8</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Aucun webp. Les PNG de fiche produit portent l'essentiel du surpoids.</t>
+          <t>Une partie intégrée en juin et juillet, à recontrôler au re-crawl.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="44" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Images</t>
+          <t>Balisage</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Balises ALT vides</t>
+          <t>Meta descriptions trop longues / manquantes</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>192 sur 334, soit 57 %</t>
+          <t>15 / 12</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Perte sèche sur Google Images et sur l'accessibilité.</t>
+          <t>Aucune description trop courte relevée.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="44" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Maillage</t>
+          <t>Balisage</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Liens internes rompus encore marqués FALSE</t>
+          <t>H1 trop longs / trop courts / manquants</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>33 sur 38</t>
+          <t>12 / 3 / 18</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Le ticket est pourtant déclaré intégré au 14/08/2026 dans la roadmap.</t>
+          <t>Les 18 manquants tiennent à 5 gabarits : 5 corrections, pas 18.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="44" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Maillage</t>
+          <t>Balisage</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Liens sortants en échec</t>
+          <t>Pages à deux H1 corrigées le 24/08/2026</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>environ 200</t>
+          <t>23 sur 23</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>404 en majorité, 22 en 410, 12 en 503, une cinquantaine d'URL invalides saisies dans le contenu.</t>
+          <t>Vérifié : la colonne « H1 count now » est à 1 sur les 23 lignes.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="44" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Maillage</t>
+          <t>Balisage</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Plan de maillage interne existant</t>
+          <t>Lignes PRODUITS du Tableau de balisage visant la mauvaise URL</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>aucun</t>
+          <t>6 sur 6</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>L'onglet « Pages orphelines » de l'extraction indexation est vide.</t>
+          <t>Elles ciblent les URL longues alors que les pages indexées sont les URL courtes.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="44" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Images</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Relevé Lighthouse par gabarit</t>
+          <t>Images relevées et poids total</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>aucun</t>
+          <t>334 pour 91,3 Mo</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Volet jamais ouvert depuis le début de l'accompagnement.</t>
+          <t>Moyenne de 273 Ko par image, très au-delà d'un gabarit e-commerce sain.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="44" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>JSON-LD</t>
+          <t>Images</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Données structurées relevées</t>
+          <t>Images au-delà de 200 Ko / de 500 Ko</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>aucune</t>
+          <t>64 / 36</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Product, Offer, Organization, BreadcrumbList et FAQPage attendus sur un site marchand.</t>
+          <t>La plus lourde atteint 3,58 Mo (PurCar_6.png).</t>
         </is>
       </c>
     </row>
     <row r="24" ht="44" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Hreflang</t>
+          <t>Images</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Audit hreflang réalisé</t>
+          <t>Formats servis</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>aucun</t>
+          <t>232 jpeg, 99 png, 3 svg</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>12 langues en production, et des pages en anglais servies sous /fr.</t>
+          <t>Aucun webp. Les PNG de fiche produit portent l'essentiel du surpoids.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="44" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Géo</t>
+          <t>Images</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Pages ville en production</t>
+          <t>Balises ALT vides</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>5 dont 1 en anglais</t>
+          <t>192 sur 334, soit 57 %</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Lyon en position 6, Paris en 18, Londres en 16, Paris EN en 7. Couche non structurée.</t>
+          <t>Perte sèche sur Google Images et sur l'accessibilité.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="44" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
+          <t>Maillage</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Liens internes rompus encore marqués FALSE</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>33 sur 38</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Le ticket est pourtant déclaré intégré au 14/08/2026 dans la roadmap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="44" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Maillage</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Liens sortants en échec</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>environ 200</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>404 en majorité, 22 en 410, 12 en 503, une cinquantaine d'URL invalides saisies dans le contenu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="44" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Maillage</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Plan de maillage interne existant</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>aucun</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>L'onglet « Pages orphelines » de l'extraction indexation est vide.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="44" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Vitesse</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Relevé Lighthouse par gabarit</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>aucun</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Volet jamais ouvert depuis le début de l'accompagnement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="44" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>JSON-LD</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Accueil, catégorie, page métier et FAQ</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>aucun type enrichi détecté</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Organization, CollectionPage, Article et FAQPage restent à poser.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="44" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Hreflang</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Audit hreflang réalisé</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>aucun</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>12 langues en production, et des pages en anglais servies sous /fr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="44" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Géo</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Pages ville en production</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>5 dont 1 en anglais</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>Lyon en position 6, Paris en 18, Londres en 16, Paris EN en 7. Couche non structurée.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="44" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
           <t>Comparatifs</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>Pages comparant Eoleaf à un concurrent</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>Fort potentiel d'achat : Levoit en position 20 sur 390, « dyson chauffant » en 9 sur 1900.</t>
         </is>

--- a/livrables/2026-09-04-roadmap-technique-septembre-eoleaf.xlsx
+++ b/livrables/2026-09-04-roadmap-technique-septembre-eoleaf.xlsx
@@ -77,12 +77,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FBE9E7"/>
+        <fgColor rgb="00FFF8E1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF8E1"/>
+        <fgColor rgb="00FBE9E7"/>
       </patternFill>
     </fill>
   </fills>
@@ -133,11 +133,11 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -588,220 +588,220 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Redirections des anciennes URL AEROPRO</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Poser les 301 des anciennes URL produit AEROPRO 40, 100 et 150 vers les fiches NeoPur 400, TeraPur 600 et AltaPur 700. Traité par Nicolas le 04/09/2026, avant l'échéance d'octobre. Le contrôle Search Console confirmait le besoin : /fr/products/aeropro-150-airpurifier ressortait en « Explorée, actuellement non indexée ». Fini quand : chaque ancienne URL répond 301 en un saut vers la fiche du modèle actuel.</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>EOLEAF</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>TERMINE</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>Redirections AEROPRO Eoleaf</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="104" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>SEPTEMBRE</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
           <t>01/09/2026</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Re-crawl de contrôle indexation</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Relancer le crawl en 1 thread et 1 URL par seconde, user-agent Googlebot Smartphone, puis confronter chaque statut à l'inspection d'URL de la Search Console sur 10 URL témoin. L'extraction du 20/05 classe environ 250 URL en erreur client alors que certaines se positionnent de la 4e à la 8e place : les deux ne peuvent pas être vrais. Ce ticket conditionne la lecture des sept autres. Fini quand : nouvel export d'indexation daté, écart crawl / Search Console expliqué ligne à ligne, ancien onglet renommé « z · Indexation 05-2026 (ancien) ».</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>SEO MONKEY</t>
         </is>
       </c>
-      <c r="F3" s="5" t="n">
+      <c r="F4" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>EN COURS</t>
-        </is>
-      </c>
-      <c r="H3" s="6" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>TERMINE</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>Controle indexation Eoleaf</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>Nicolas</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="104" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+    <row r="5" ht="104" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>SEPTEMBRE</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>01/09/2026</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Canonique des fiches produit</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Retenir une seule forme d'URL indexable par produit, poser la canonique autoréférente dessus et aligner les liens internes. Les pages indexées sont en /fr/products/ alors que l'onglet « Tableau de balisage » prépare les titles sur les URL en /fr/collections/.../products/ : intégré en l'état, ce balisage se pose à côté des pages qui rankent. Fini quand : une seule URL par produit répond 200 sans redirection, canonique autoréférente, et l'onglet « Tableau de balisage » corrigé avant intégration.</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>SEO MONKEY</t>
         </is>
       </c>
-      <c r="F4" s="5" t="n">
+      <c r="F5" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>A FAIRE</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>Canonique fiches produit Eoleaf</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>Nicolas</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="104" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="6" ht="104" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>SEPTEMBRE</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>08/09/2026</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Lien FAQ vers un formulaire SAV mort</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Poser une 301 de /fr/pages/formulaire-apres-vente vers /fr/pages/formulaire-sav et corriger le lien depuis /fr/pages/faqs. Périmètre réduit par le contrôle Search Console du 04/09 : les pages contact FR, EN et DE sont indexées et saines, la FR est même en position 2,2 avec 477 impressions. Le crawl du 20/05 les déclarait en erreur à tort. Seule l'URL formulaire-apres-vente est réellement morte. Fini quand : /fr/pages/formulaire-apres-vente répond 301 vers formulaire-sav, et la FAQ pointe directement vers l'URL vivante.</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>EOLEAF</t>
         </is>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="F6" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>A FAIRE</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>Contact et SAV 12 langues Eoleaf</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>Eoleaf</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="104" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+    <row r="7" ht="104" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>SEPTEMBRE</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>08/09/2026</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>36 pages EN sous le préfixe /fr</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>Rediriger en 301 les 36 URL anglaises servies sous /fr : vers la page FR équivalente quand elle existe, sinon vers l'URL anglaise à la racine. Défaut de l'application de traduction : la page existe en double et Google reçoit de l'anglais sur une URL déclarée française. Trois anciennes fiches AEROPRO sont dans le lot. Fini quand : les 36 URL répondent 301 en un saut vers la bonne cible, et aucune ne figure plus au sitemap.</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>SEO MONKEY + EOLEAF</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>36 pages EN sous /fr : budget de crawl</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Rediriger en 301 les 36 URL anglaises servies sous /fr : vers la page FR équivalente quand elle existe, sinon vers l'URL anglaise à la racine. Périmètre revu par le contrôle Search Console du 04/09 : sur les 33 de ces URL sans impression, 28 ressortent en « Google ne reconnaît pas cette URL ». Elles ne sont donc pas indexées et ne cannibalisent rien. Ce qu'elles coûtent : du budget de crawl, et des liens internes qui partent dans le vide. Le ticket reste utile mais n'est plus bloquant, et son volume baisse. Fini quand : les 36 URL répondent 301 en un saut vers la bonne cible, et aucune ne figure plus au sitemap ni dans un lien interne.</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>EOLEAF</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>A FAIRE</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>Pages EN sous prefixe fr Eoleaf</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>Nicolas / Eoleaf</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="104" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>SEPTEMBRE</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>15/09/2026</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Cannibalisation : 14 clusters FR</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Désigner un pilier par cluster, fusionner les doublons d'intention dans ce pilier puis poser les 301. L'onglet sémantique en porte la preuve : « purificateur d'air voiture » est planifié sur 3 URL, « purificateur d'air chambre » sur 2, « allergie chat » sur 2, « fumée de cigarette » sur 2. Le cluster dentaire compte 3 pages sur la même intention, le cluster tabac 5. Fini quand : un seul pilier par cluster, contenu utile remonté avant la 301, aucune page en top 3 touchée.</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>SEO MONKEY</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>A FAIRE</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>Cannibalisation clusters FR Eoleaf</t>
-        </is>
-      </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>Jordan / Nicolas</t>
+          <t>Eoleaf</t>
         </is>
       </c>
     </row>
@@ -813,141 +813,186 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Cannibalisation : 14 clusters FR</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Désigner un pilier par cluster, fusionner les doublons d'intention dans ce pilier puis poser les 301. L'onglet sémantique en porte la preuve : « purificateur d'air voiture » est planifié sur 3 URL, « purificateur d'air chambre » sur 2, « allergie chat » sur 2, « fumée de cigarette » sur 2. Le cluster dentaire compte 3 pages sur la même intention, le cluster tabac 5. Fini quand : un seul pilier par cluster, contenu utile remonté avant la 301, aucune page en top 3 touchée.</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>SEO MONKEY</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>A FAIRE</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>Cannibalisation clusters FR Eoleaf</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>Jordan / Nicolas</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="104" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SEPTEMBRE</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
           <t>22/09/2026</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>33 liens internes rompus</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Corriger les 33 lignes encore marquées « Réglé ? = FALSE » dans le fichier existant, alors que le ticket est déclaré intégré au 14/08. Deux cibles mortes reviennent sur les 12 langues. La colonne « Newlink » porte déjà la cible de remplacement : il n'y a pas de mapping à refaire. Fini quand : zéro ligne FALSE, et les 38 liens répondent 200 en un seul saut.</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>EOLEAF</t>
         </is>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F9" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>A FAIRE</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>liens internes rompus</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>Eoleaf</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="104" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
+    <row r="10" ht="104" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>SEPTEMBRE</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>22/09/2026</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>H1 manquants sur 5 gabarits</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>Poser un H1 unique sur les gabarits qui en sont dépourvus : collection, institutionnel, page métier, comparatif et FAQ. 18 H1 manquants et 12 trop longs relevés, mais 5 corrections de gabarit Shopify suffisent et traitent les 12 langues d'un seul geste. Les H1 sont déjà rédigés dans le livrable. Fini quand : un H1 et un seul par page, de 20 à 70 caractères, contenant l'expression cible, et zéro statut « Manquant » au re-crawl.</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>SEO MONKEY + EOLEAF</t>
         </is>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="F10" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>A FAIRE</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>H1 manquants Eoleaf</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>Jordan / Eoleaf</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="104" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
+    <row r="11" ht="104" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>SEPTEMBRE</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>29/09/2026</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>Images des gabarits d'achat</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>Convertir en webp et recompresser les images de l'accueil, de la collection et de la fiche produit, puis renseigner les ALT. 334 images pour 91,3 Mo, 64 au-delà de 200 Ko, 36 au-delà de 500 Ko, 99 PNG, aucun webp, et 192 ALT vides sur 334. Les plus lourdes sont des visuels de fiche produit, entre 2,7 et 3,6 Mo. Les ALT sont déjà rédigés dans le livrable. Fini quand : aucune image servie au-delà de 200 Ko sur ces trois gabarits, largeur servie ≤ 1500 px, zéro ALT vide, LCP mobile de la fiche produit sous 2,5 s.</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>SEO MONKEY + EOLEAF</t>
         </is>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="F11" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>A FAIRE</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>Images a corriger Eoleaf</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>Jordan / Eoleaf</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="E11" s="8" t="inlineStr">
+    <row r="12">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>TOTAL SEPTEMBRE</t>
         </is>
       </c>
-      <c r="F11" s="8" t="n">
-        <v>26.5</v>
+      <c r="F12" s="9" t="n">
+        <v>25.5</v>
       </c>
     </row>
   </sheetData>
@@ -964,6 +1009,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -975,7 +1021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1052,7 +1098,7 @@
       <c r="I2" s="3" t="n"/>
     </row>
     <row r="3" ht="104" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>OCTOBRE</t>
         </is>
@@ -1097,24 +1143,24 @@
       </c>
     </row>
     <row r="4" ht="104" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>OCTOBRE</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Redirections des anciennes URL AEROPRO</t>
+          <t>Doublons de pages de service</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Poser les 301 des anciennes URL produit AEROPRO 40, 100 et 150 vers les fiches NeoPur 400, TeraPur 600 et AltaPur 700. Ces URL circulent encore et reçoivent des liens internes : sans 301, l'autorité est perdue et le visiteur tombe sur une page morte. Fini quand : chaque ancienne URL répond 301 en un saut vers la fiche du modèle actuel.</t>
+          <t>Fusionner les pages de service existant en deux exemplaires, l'une au slug français, l'autre au slug anglais sous le même préfixe : garantie, SAV, photos clients, Belgique, ozone. Fini quand : une seule URL par service répond 200, le doublon répond 301, et les liens internes pointent vers la page conservée.</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -1123,7 +1169,7 @@
         </is>
       </c>
       <c r="F4" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
@@ -1132,7 +1178,7 @@
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>Redirections AEROPRO Eoleaf</t>
+          <t>Doublons pages service Eoleaf</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
@@ -1142,29 +1188,29 @@
       </c>
     </row>
     <row r="5" ht="104" customHeight="1">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>OCTOBRE</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Doublons de pages de service</t>
+          <t>Vitesse par gabarit</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Fusionner les pages de service existant en deux exemplaires, l'une au slug français, l'autre au slug anglais sous le même préfixe : garantie, SAV, photos clients, Belgique, ozone. Fini quand : une seule URL par service répond 200, le doublon répond 301, et les liens internes pointent vers la page conservée.</t>
+          <t>Relever Lighthouse mobile sur un exemplaire de chacun des 6 gabarits : accueil, collection, fiche produit, page métier, question, géo. Aucune mesure de vitesse n'existe à ce jour dans le dossier. Fini quand : LCP, INP et CLS relevés et datés pour les 6 gabarits, et un ticket ouvert par gabarit hors seuil.</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>EOLEAF</t>
+          <t>SEO MONKEY</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
@@ -1177,314 +1223,314 @@
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>Doublons pages service Eoleaf</t>
+          <t>Vitesse par gabarit Eoleaf</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>Eoleaf</t>
+          <t>Nicolas</t>
         </is>
       </c>
     </row>
     <row r="6" ht="104" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>OCTOBRE</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>27/10/2026</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Vitesse par gabarit</t>
+          <t>JSON-LD hors fiche produit</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Relever Lighthouse mobile sur un exemplaire de chacun des 6 gabarits : accueil, collection, fiche produit, page métier, question, géo. Aucune mesure de vitesse n'existe à ce jour dans le dossier. Fini quand : LCP, INP et CLS relevés et datés pour les 6 gabarits, et un ticket ouvert par gabarit hors seuil.</t>
+          <t>Écrire et intégrer le balisage de données structurées pour l'accueil (Organization, WebSite), la catégorie (CollectionPage, ItemList), les pages métier (Article, Person) et la FAQ (FAQPage). Périmètre réduit par le contrôle Search Console du 04/09 : la fiche produit porte déjà Product, Offer et AggregateRating, verdict PASS, avec extraits de produit, fiche de marchand et extraits d'avis détectés. Réserve : l'inspection d'URL ne remonte que les types éligibles aux résultats enrichis, l'absence de BreadcrumbList reste à confirmer dans le code des gabarits. Fini quand : le test des résultats enrichis ne remonte aucune erreur sur les quatre gabarits restants.</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
+          <t>SEO MONKEY + EOLEAF</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>A FAIRE</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>JSON-LD par gabarit Eoleaf</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>Nicolas / Eoleaf</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="104" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>OCTOBRE</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>27/10/2026</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Sitemap contre pages réelles</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Confronter le sitemap aux pages du re-crawl : indexables absentes du sitemap, et URL déclarées qui ne répondent pas 200. Vérifier aussi la couverture des 12 langues et la déclaration dans robots.txt. Fini quand : chaque URL du sitemap répond 200 et est canonique, et chaque page indexable y figure.</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
           <t>SEO MONKEY</t>
         </is>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F7" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>A FAIRE</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>Vitesse par gabarit Eoleaf</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>Sitemap contre pages Eoleaf</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>Nicolas</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="104" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>OCTOBRE</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>27/10/2026</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>JSON-LD hors fiche produit</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Écrire et intégrer le balisage de données structurées pour l'accueil (Organization, WebSite), la catégorie (CollectionPage, ItemList), les pages métier (Article, Person) et la FAQ (FAQPage). Périmètre réduit par le contrôle Search Console du 04/09 : la fiche produit porte déjà Product, Offer et AggregateRating, verdict PASS, avec extraits de produit, fiche de marchand et extraits d'avis détectés. Réserve : l'inspection d'URL ne remonte que les types éligibles aux résultats enrichis, l'absence de BreadcrumbList reste à confirmer dans le code des gabarits. Fini quand : le test des résultats enrichis ne remonte aucune erreur sur les quatre gabarits restants.</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
+    <row r="8">
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>TOTAL OCTOBRE</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" ht="104" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>NOVEMBRE</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>03/11/2026</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Robots.txt et URL à paramètres</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Fermer au crawl la recherche interne, le panier, /apps/ et les URL en ?q=, ?srsltid=, ?redirected=. Ces URL consomment du budget de crawl sans rien rapporter. La pagination de collection, elle, reste ouverte. Fini quand : robots.txt.liquid à jour, sitemap déclaré dedans, et ces URL absentes du crawl suivant.</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>SEO MONKEY + EOLEAF</t>
         </is>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A FAIRE</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>Robots et parametres Eoleaf</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Nicolas / Eoleaf</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="104" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>NOVEMBRE</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>03/11/2026</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Liens sortants rompus</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Remplacer les sources citées qui ne répondent plus, pages FR à impressions d'abord. Environ 200 liens sortants en échec : 404 en majorité, 22 en 410, 12 en 503, et une cinquantaine d'URL invalides saisies dans le contenu. Chaque erreur étant répliquée sur 12 langues, une correction en français se propage. Fini quand : zéro lien sortant en erreur sur les pages FR à impressions, chaque source morte remplacée par une source vivante équivalente.</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>SEO MONKEY + EOLEAF</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>A FAIRE</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>JSON-LD par gabarit Eoleaf</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>Nicolas / Eoleaf</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="104" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>OCTOBRE</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>27/10/2026</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>Sitemap contre pages réelles</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>Confronter le sitemap aux pages du re-crawl : indexables absentes du sitemap, et URL déclarées qui ne répondent pas 200. Vérifier aussi la couverture des 12 langues et la déclaration dans robots.txt. Fini quand : chaque URL du sitemap répond 200 et est canonique, et chaque page indexable y figure.</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>Liens sortants a remplacer Eoleaf</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>Jordan / Eoleaf</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="104" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>NOVEMBRE</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>10/11/2026</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Plan de maillage interne</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Construire la carte des silos et le plan de liens ligne à ligne, à partir du cocon sémantique XMind. Volet jamais produit : la quarantaine de pages métier n'est pas câblée vers les fiches produit. Vérifier les liens déjà posés avant de proposer quoi que ce soit. Fini quand : carte XMind livrée, et plan portant pour chaque lien la source, la destination, l'ancre en exact match et la mention « déjà posé ».</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>SEO MONKEY</t>
         </is>
       </c>
-      <c r="F8" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="F11" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>A FAIRE</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>Sitemap contre pages Eoleaf</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>Plan de maillage Eoleaf</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>Nicolas</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>TOTAL OCTOBRE</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" ht="104" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
+    <row r="12" ht="104" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>NOVEMBRE</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>03/11/2026</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Robots.txt et URL à paramètres</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>Fermer au crawl la recherche interne, le panier, /apps/ et les URL en ?q=, ?srsltid=, ?redirected=. Ces URL consomment du budget de crawl sans rien rapporter. La pagination de collection, elle, reste ouverte. Fini quand : robots.txt.liquid à jour, sitemap déclaré dedans, et ces URL absentes du crawl suivant.</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>SEO MONKEY + EOLEAF</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>10/11/2026</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Profondeur et pages orphelines</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Sortir la distribution des pages par niveau de clic, la liste des pages d'achat au-delà du niveau 3, et les orphelines croisées avec les impressions. L'onglet « Pages orphelines » est resté vide depuis le début. Fini quand : aucune page d'achat au-delà du niveau 3, et chaque orpheline reçoit un lien interne ou est fusionnée.</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>SEO MONKEY</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>A FAIRE</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>Robots et parametres Eoleaf</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>Nicolas / Eoleaf</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="104" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Profondeur et orphelines Eoleaf</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="104" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>NOVEMBRE</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>03/11/2026</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Liens sortants rompus</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>Remplacer les sources citées qui ne répondent plus, pages FR à impressions d'abord. Environ 200 liens sortants en échec : 404 en majorité, 22 en 410, 12 en 503, et une cinquantaine d'URL invalides saisies dans le contenu. Chaque erreur étant répliquée sur 12 langues, une correction en français se propage. Fini quand : zéro lien sortant en erreur sur les pages FR à impressions, chaque source morte remplacée par une source vivante équivalente.</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>SEO MONKEY + EOLEAF</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>A FAIRE</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>Liens sortants a remplacer Eoleaf</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>Jordan / Eoleaf</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="104" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>NOVEMBRE</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>10/11/2026</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Plan de maillage interne</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>Construire la carte des silos et le plan de liens ligne à ligne, à partir du cocon sémantique XMind. Volet jamais produit : la quarantaine de pages métier n'est pas câblée vers les fiches produit. Vérifier les liens déjà posés avant de proposer quoi que ce soit. Fini quand : carte XMind livrée, et plan portant pour chaque lien la source, la destination, l'ancre en exact match et la mention « déjà posé ».</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>SEO MONKEY</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>A FAIRE</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>Plan de maillage Eoleaf</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>Nicolas</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="104" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>NOVEMBRE</t>
-        </is>
-      </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>10/11/2026</t>
+          <t>17/11/2026</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Profondeur et pages orphelines</t>
+          <t>Couche géo : 4 pages villes</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Sortir la distribution des pages par niveau de clic, la liste des pages d'achat au-delà du niveau 3, et les orphelines croisées avec les impressions. L'onglet « Pages orphelines » est resté vide depuis le début. Fini quand : aucune page d'achat au-delà du niveau 3, et chaque orpheline reçoit un lien interne ou est fusionnée.</t>
+          <t>Trancher le statut de la couche géo, puis aligner les 4 pages ville sur un gabarit commun et les câbler au pilier professionnel. Lyon est en position 6 et Paris en 18 : la couche produit déjà du trafic sans être structurée. Deux slugs portent une phrase entière, dont une faute de frappe. Fini quand : les 4 pages partagent le même gabarit, portent un lien vers l'unité d'achat, et les slugs fautifs sont corrigés avec 301.</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1502,153 +1548,108 @@
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>Profondeur et orphelines Eoleaf</t>
+          <t>Pages geo villes Eoleaf</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="104" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>NOVEMBRE</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>24/11/2026</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>13 comparatifs concurrents</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Aligner les pages comparatives sur un gabarit commun : tableau chiffré, preuve vérifiable, mention honnête d'un point où le concurrent est meilleur, et lien vers la fiche produit. Ce sont des pages à forte intention d'achat. Levoit est en position 20 sur 390 de volume, « dyson chauffant » en 9 sur 1900. Fini quand : chaque comparatif porte les 4 modules et un lien vers la fiche du modèle Eoleaf comparé.</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>SEO MONKEY</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>A FAIRE</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>Comparatifs concurrents Eoleaf</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="104" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>NOVEMBRE</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>24/11/2026</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Maquettes SXO par étage</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Produire une maquette par étage de l'arbre : hub de silo, collection, fiche produit, page question. À la charte Eoleaf, avec les sections de preuve et les liens du plan de maillage posés au bon endroit. Fini quand : une maquette HTML par étage, reprenant le contenu réel de la page capturée, et respectant le plan de maillage.</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>SEO MONKEY</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>A FAIRE</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
           <t>Nicolas</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="104" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>NOVEMBRE</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>17/11/2026</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Couche géo : 4 pages villes</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>Trancher le statut de la couche géo, puis aligner les 4 pages ville sur un gabarit commun et les câbler au pilier professionnel. Lyon est en position 6 et Paris en 18 : la couche produit déjà du trafic sans être structurée. Deux slugs portent une phrase entière, dont une faute de frappe. Fini quand : les 4 pages partagent le même gabarit, portent un lien vers l'unité d'achat, et les slugs fautifs sont corrigés avec 301.</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>SEO MONKEY</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>A FAIRE</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>Pages geo villes Eoleaf</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="104" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>NOVEMBRE</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>24/11/2026</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>13 comparatifs concurrents</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>Aligner les pages comparatives sur un gabarit commun : tableau chiffré, preuve vérifiable, mention honnête d'un point où le concurrent est meilleur, et lien vers la fiche produit. Ce sont des pages à forte intention d'achat. Levoit est en position 20 sur 390 de volume, « dyson chauffant » en 9 sur 1900. Fini quand : chaque comparatif porte les 4 modules et un lien vers la fiche du modèle Eoleaf comparé.</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>SEO MONKEY</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>A FAIRE</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>Comparatifs concurrents Eoleaf</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="104" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>NOVEMBRE</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>24/11/2026</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>Maquettes SXO par étage</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>Produire une maquette par étage de l'arbre : hub de silo, collection, fiche produit, page question. À la charte Eoleaf, avec les sections de preuve et les liens du plan de maillage posés au bon endroit. Fini quand : une maquette HTML par étage, reprenant le contenu réel de la page capturée, et respectant le plan de maillage.</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>SEO MONKEY</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>A FAIRE</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="n"/>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>Nicolas</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="E17" s="8" t="inlineStr">
+    <row r="16">
+      <c r="E16" s="9" t="inlineStr">
         <is>
           <t>TOTAL NOVEMBRE</t>
         </is>
       </c>
-      <c r="F17" s="8" t="n">
+      <c r="F16" s="9" t="n">
         <v>28</v>
       </c>
     </row>
@@ -1663,13 +1664,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1681,7 +1681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1752,17 +1752,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>URL témoin déclarées indexées par Google</t>
+          <t>URL déclarées non indexées au crawl qui portent en réalité des impressions</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>10 sur 10</t>
+          <t>206 sur 305</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Inspection d'URL du 04/09. Les 6 classées « erreur client » au crawl sont saines : robots autorisé, page récupérée, dernier passage de Google entre le 22/08 et le 04/09.</t>
+          <t>Soit 68 %, cumulant 5 748 clics et 562 617 impressions sur 90 jours. Écart expliqué ligne à ligne dans l'onglet ECART CRAWL 05-2026 du nouvel export.</t>
         </is>
       </c>
     </row>
@@ -1774,17 +1774,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Clics et impressions sur 90 jours</t>
+          <t>URL sans impression inspectées une à une</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>28 889 · 3 765 160</t>
+          <t>99</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Position moyenne 12,5. Le site est massivement indexé et visible.</t>
+          <t>68 inconnues de Google (formes d'URL parasites), 21 explorées non indexées, 6 déjà redirigées, 2 indexées sans impression, 2 canoniques ou noindex volontaires.</t>
         </is>
       </c>
     </row>
@@ -1796,17 +1796,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Part du français dans les clics</t>
+          <t>URL non couvertes par un ticket existant</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>21 %</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>284 pages FR pour 6 106 clics. Les onze autres langues portent 79 % des clics : la priorisation par langue est à revoir avec Eoleaf.</t>
+          <t>Dont 3 unités d'achat FR explorées et non indexées. Listées dans l'onglet A ARBITRER.</t>
         </is>
       </c>
     </row>
@@ -1818,17 +1818,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Page la plus cliquée du site</t>
+          <t>Slugs anglais sous /fr que Google ne connaît pas</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>/de/pages/kauf-eines-luftreinigers-fur-cannabis</t>
+          <t>28 sur 33</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>928 clics et 10 216 impressions sur 90 jours. Elle est en allemand.</t>
+          <t>Ces URL ne cannibalisent rien : le ticket passe de bloquant à budget de crawl, de 4 h à 2 h.</t>
         </is>
       </c>
     </row>
@@ -1840,17 +1840,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>URL témoin absentes du sitemap</t>
+          <t>Recherche interne /fr/search</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>6 sur 10</t>
+          <t>indexée</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Dont l'accueil FR, la fiche AltaPur 700 et deux unités d'achat. Elles rankent sans être déclarées.</t>
+          <t>Confirmée « Envoyée et indexée ». Le ticket robots.txt est justifié.</t>
         </is>
       </c>
     </row>
@@ -1862,61 +1862,61 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>URL déclarées au sitemap</t>
+          <t>URL témoin déclarées indexées par Google</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>3 001</t>
+          <t>10 sur 10</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Dernier téléchargement par Google le 03/09/2026, zéro erreur, zéro avertissement.</t>
+          <t>Inspection d'URL du 04/09. Les 6 classées « erreur client » au crawl sont saines : robots autorisé, page récupérée, dernier passage de Google entre le 22/08 et le 04/09.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="44" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Sémantique</t>
+          <t>Indexation</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Écart de position relevé sur l'onglet sémantique</t>
+          <t>Clics et impressions sur 90 jours</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>position 4 contre 37</t>
+          <t>28 889 · 3 765 160</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>« purificateur d'air professionnel » : l'onglet donne 4, la Search Console 37 avec 894 impressions et 3 clics. Les positions de l'onglet sémantique sont à re-sourcer.</t>
+          <t>Position moyenne 12,5. Le site est massivement indexé et visible.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="44" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>JSON-LD</t>
+          <t>Indexation</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Fiche produit</t>
+          <t>Part du français dans les clics</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Product, Offer et AggregateRating présents</t>
+          <t>21 %</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Verdict PASS au 04/09. Le gabarit qui encaisse est déjà équipé, contrairement au constat initial.</t>
+          <t>284 pages FR pour 6 106 clics. Les onze autres langues portent 79 % des clics : la priorisation par langue est à revoir avec Eoleaf.</t>
         </is>
       </c>
     </row>
@@ -1928,17 +1928,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Versions linguistiques du site</t>
+          <t>Page la plus cliquée du site</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>/de/pages/kauf-eines-luftreinigers-fur-cannabis</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>fr, en à la racine, da, de, es, fi, it, nl, no, pl, ro, sv. Une correction de gabarit se propage.</t>
+          <t>928 clics et 10 216 impressions sur 90 jours. Elle est en allemand.</t>
         </is>
       </c>
     </row>
@@ -1950,17 +1950,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>URL anglaises servies sous le préfixe /fr</t>
+          <t>URL témoin absentes du sitemap</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>6 sur 10</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Duplication et mauvaise langue déclarée. Défaut de l'application de traduction.</t>
+          <t>Dont l'accueil FR, la fiche AltaPur 700 et deux unités d'achat. Elles rankent sans être déclarées.</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Anciennes URL produit AEROPRO encore en circulation</t>
+          <t>URL déclarées au sitemap</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3 001</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>La gamme a été renommée NeoPur, TeraPur, AltaPur sans que les 301 soient posées.</t>
+          <t>Dernier téléchargement par Google le 03/09/2026, zéro erreur, zéro avertissement.</t>
         </is>
       </c>
     </row>
@@ -1994,411 +1994,521 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Clusters FR où deux pages ou plus visent la même intention</t>
+          <t>Écart de position relevé sur l'onglet sémantique</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>position 4 contre 37</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Le cluster tabac compte 5 pages, le dentaire 3, la voiture 4. Un pilier par cluster à désigner.</t>
+          <t>« purificateur d'air professionnel » : l'onglet donne 4, la Search Console 37 avec 894 impressions et 3 clics. Les positions de l'onglet sémantique sont à re-sourcer.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="44" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Sémantique</t>
+          <t>JSON-LD</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Requêtes de l'onglet sémantique planifiées sur plusieurs URL</t>
+          <t>Fiche produit</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>4 au moins</t>
+          <t>Product, Offer et AggregateRating présents</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Voiture sur 3 URL, chambre sur 2, allergie chat sur 2, fumée de cigarette sur 2.</t>
+          <t>Verdict PASS au 04/09. Le gabarit qui encaisse est déjà équipé, contrairement au constat initial.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="44" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Balisage</t>
+          <t>Indexation</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Meta titles trop longs / trop courts / manquants</t>
+          <t>Versions linguistiques du site</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>11 / 13 / 8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Une partie intégrée en juin et juillet, à recontrôler au re-crawl.</t>
+          <t>fr, en à la racine, da, de, es, fi, it, nl, no, pl, ro, sv. Une correction de gabarit se propage.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="44" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Balisage</t>
+          <t>Indexation</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Meta descriptions trop longues / manquantes</t>
+          <t>URL anglaises servies sous le préfixe /fr</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>15 / 12</t>
+          <t>36</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Aucune description trop courte relevée.</t>
+          <t>Duplication et mauvaise langue déclarée. Défaut de l'application de traduction.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="44" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Balisage</t>
+          <t>Indexation</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>H1 trop longs / trop courts / manquants</t>
+          <t>Anciennes URL produit AEROPRO encore en circulation</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>12 / 3 / 18</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Les 18 manquants tiennent à 5 gabarits : 5 corrections, pas 18.</t>
+          <t>La gamme a été renommée NeoPur, TeraPur, AltaPur sans que les 301 soient posées.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="44" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Balisage</t>
+          <t>Sémantique</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Pages à deux H1 corrigées le 24/08/2026</t>
+          <t>Clusters FR où deux pages ou plus visent la même intention</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>23 sur 23</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Vérifié : la colonne « H1 count now » est à 1 sur les 23 lignes.</t>
+          <t>Le cluster tabac compte 5 pages, le dentaire 3, la voiture 4. Un pilier par cluster à désigner.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="44" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Balisage</t>
+          <t>Sémantique</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Lignes PRODUITS du Tableau de balisage visant la mauvaise URL</t>
+          <t>Requêtes de l'onglet sémantique planifiées sur plusieurs URL</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>6 sur 6</t>
+          <t>4 au moins</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Elles ciblent les URL longues alors que les pages indexées sont les URL courtes.</t>
+          <t>Voiture sur 3 URL, chambre sur 2, allergie chat sur 2, fumée de cigarette sur 2.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="44" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Images</t>
+          <t>Balisage</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Images relevées et poids total</t>
+          <t>Meta titles trop longs / trop courts / manquants</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>334 pour 91,3 Mo</t>
+          <t>11 / 13 / 8</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Moyenne de 273 Ko par image, très au-delà d'un gabarit e-commerce sain.</t>
+          <t>Une partie intégrée en juin et juillet, à recontrôler au re-crawl.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="44" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Images</t>
+          <t>Balisage</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Images au-delà de 200 Ko / de 500 Ko</t>
+          <t>Meta descriptions trop longues / manquantes</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>64 / 36</t>
+          <t>15 / 12</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>La plus lourde atteint 3,58 Mo (PurCar_6.png).</t>
+          <t>Aucune description trop courte relevée.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="44" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Images</t>
+          <t>Balisage</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Formats servis</t>
+          <t>H1 trop longs / trop courts / manquants</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>232 jpeg, 99 png, 3 svg</t>
+          <t>12 / 3 / 18</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Aucun webp. Les PNG de fiche produit portent l'essentiel du surpoids.</t>
+          <t>Les 18 manquants tiennent à 5 gabarits : 5 corrections, pas 18.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="44" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Images</t>
+          <t>Balisage</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Balises ALT vides</t>
+          <t>Pages à deux H1 corrigées le 24/08/2026</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>192 sur 334, soit 57 %</t>
+          <t>23 sur 23</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Perte sèche sur Google Images et sur l'accessibilité.</t>
+          <t>Vérifié : la colonne « H1 count now » est à 1 sur les 23 lignes.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="44" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Maillage</t>
+          <t>Balisage</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Liens internes rompus encore marqués FALSE</t>
+          <t>Lignes PRODUITS du Tableau de balisage visant la mauvaise URL</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>33 sur 38</t>
+          <t>6 sur 6</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Le ticket est pourtant déclaré intégré au 14/08/2026 dans la roadmap.</t>
+          <t>Elles ciblent les URL longues alors que les pages indexées sont les URL courtes.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="44" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Maillage</t>
+          <t>Images</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Liens sortants en échec</t>
+          <t>Images relevées et poids total</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>environ 200</t>
+          <t>334 pour 91,3 Mo</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>404 en majorité, 22 en 410, 12 en 503, une cinquantaine d'URL invalides saisies dans le contenu.</t>
+          <t>Moyenne de 273 Ko par image, très au-delà d'un gabarit e-commerce sain.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="44" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Maillage</t>
+          <t>Images</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Plan de maillage interne existant</t>
+          <t>Images au-delà de 200 Ko / de 500 Ko</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>aucun</t>
+          <t>64 / 36</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>L'onglet « Pages orphelines » de l'extraction indexation est vide.</t>
+          <t>La plus lourde atteint 3,58 Mo (PurCar_6.png).</t>
         </is>
       </c>
     </row>
     <row r="29" ht="44" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Images</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Relevé Lighthouse par gabarit</t>
+          <t>Formats servis</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>aucun</t>
+          <t>232 jpeg, 99 png, 3 svg</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Volet jamais ouvert depuis le début de l'accompagnement.</t>
+          <t>Aucun webp. Les PNG de fiche produit portent l'essentiel du surpoids.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="44" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>JSON-LD</t>
+          <t>Images</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Accueil, catégorie, page métier et FAQ</t>
+          <t>Balises ALT vides</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>aucun type enrichi détecté</t>
+          <t>192 sur 334, soit 57 %</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Organization, CollectionPage, Article et FAQPage restent à poser.</t>
+          <t>Perte sèche sur Google Images et sur l'accessibilité.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="44" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Hreflang</t>
+          <t>Maillage</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Audit hreflang réalisé</t>
+          <t>Liens internes rompus encore marqués FALSE</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>aucun</t>
+          <t>33 sur 38</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>12 langues en production, et des pages en anglais servies sous /fr.</t>
+          <t>Le ticket est pourtant déclaré intégré au 14/08/2026 dans la roadmap.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="44" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>Géo</t>
+          <t>Maillage</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Pages ville en production</t>
+          <t>Liens sortants en échec</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>5 dont 1 en anglais</t>
+          <t>environ 200</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Lyon en position 6, Paris en 18, Londres en 16, Paris EN en 7. Couche non structurée.</t>
+          <t>404 en majorité, 22 en 410, 12 en 503, une cinquantaine d'URL invalides saisies dans le contenu.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="44" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
         <is>
+          <t>Maillage</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Plan de maillage interne existant</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>aucun</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>L'onglet « Pages orphelines » de l'extraction indexation est vide.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="44" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Vitesse</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Relevé Lighthouse par gabarit</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>aucun</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Volet jamais ouvert depuis le début de l'accompagnement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="44" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>JSON-LD</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Accueil, catégorie, page métier et FAQ</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>aucun type enrichi détecté</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Organization, CollectionPage, Article et FAQPage restent à poser.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="44" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Hreflang</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Audit hreflang réalisé</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>aucun</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>12 langues en production, et des pages en anglais servies sous /fr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="44" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Géo</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Pages ville en production</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>5 dont 1 en anglais</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Lyon en position 6, Paris en 18, Londres en 16, Paris EN en 7. Couche non structurée.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="44" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
           <t>Comparatifs</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>Pages comparant Eoleaf à un concurrent</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>Fort potentiel d'achat : Levoit en position 20 sur 390, « dyson chauffant » en 9 sur 1900.</t>
         </is>
